--- a/dashboard/mpi_2024_ev_dev_combined.xlsx
+++ b/dashboard/mpi_2024_ev_dev_combined.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshuasamuel/Documents/GitHub/MPI/dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshuasamuel/Library/CloudStorage/GoogleDrive-joshua.l.samuel@gmail.com/My Drive/EV_Engine/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42DABDDA-7F56-E44F-B6AC-98AF970CC892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CD77247-399E-2644-A2E5-039F80D23CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="1800" windowWidth="27980" windowHeight="17440" xr2:uid="{AC115FC5-FD80-0941-957D-498076E5038A}"/>
+    <workbookView xWindow="5200" yWindow="1800" windowWidth="27980" windowHeight="17440" xr2:uid="{C7598ACB-5D63-D242-B45E-067F762C9FAA}"/>
   </bookViews>
   <sheets>
     <sheet name="mpi_2024_ev_dev_combined" sheetId="1" r:id="rId1"/>
@@ -3144,7 +3144,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03FDE201-2A70-ED41-93CE-3DA07260D8E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B05F75-8421-2744-BB33-173E1D7DF7C2}">
   <dimension ref="A1:AX364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <sheetData>
